--- a/artifacts/关键标准答案.xlsx
+++ b/artifacts/关键标准答案.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交付物答案清单" sheetId="1" r:id="Rf0c9ddedc95d44ba"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定字段答案" sheetId="2" r:id="R383ccd3300714613"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定集合答案" sheetId="3" r:id="R18766ba687774d4d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定数值答案" sheetId="4" r:id="R0816094faac14f23"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="允许变体答案" sheetId="5" r:id="R40c9b70a170044eb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交付物答案清单" sheetId="1" r:id="Rd717dfb9dbe0453a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定字段答案" sheetId="2" r:id="R1be5091f6c824b1a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定集合答案" sheetId="3" r:id="Rfbdddef0980348fd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定数值答案" sheetId="4" r:id="Re35208a6fc374c36"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="允许变体答案" sheetId="5" r:id="R566c299136da4c10"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -17,10 +17,6 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="2">
-    <x:numFmt numFmtId="200" formatCode="@"/>
-    <x:numFmt numFmtId="201" formatCode="yyyy-mm-dd&quot;T&quot;hh:mm:ss&quot;Z&quot;"/>
-  </x:numFmts>
   <x:fonts count="3">
     <x:font>
       <x:sz val="11"/>
@@ -89,7 +85,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="23">
+  <x:cellXfs count="16">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -123,27 +119,6 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="200" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="200" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="200" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="201" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="right" vertical="top" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="right" vertical="top" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="right" vertical="top" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -470,7 +445,7 @@
         <x:v>路径固定</x:v>
       </x:c>
       <x:c r="E7" s="13" t="str">
-        <x:v>本次回归的控制数与场景状态</x:v>
+        <x:v>本次回归的场景结果与证据索引</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="38" customHeight="1">
@@ -518,8 +493,8 @@
   <x:cols>
     <x:col min="1" max="1" width="36" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="50" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="32" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="36" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="64" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="44" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
@@ -530,150 +505,136 @@
         <x:v>字段路径</x:v>
       </x:c>
       <x:c r="C1" s="6" t="str">
-        <x:v>正确值</x:v>
+        <x:v>判定方法</x:v>
       </x:c>
       <x:c r="D1" s="6" t="str">
-        <x:v>来源</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" ht="40" customHeight="1">
+        <x:v>业务依据</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="44" customHeight="1">
       <x:c r="A2" s="14" t="str">
         <x:v>case_results.csv</x:v>
       </x:c>
       <x:c r="B2" s="14" t="str">
-        <x:v>P01的final_state</x:v>
-      </x:c>
-      <x:c r="C2" s="16" t="str">
-        <x:v>ready</x:v>
+        <x:v>final_state</x:v>
+      </x:c>
+      <x:c r="C2" s="14" t="str">
+        <x:v>按case_id与场景表的状态列比对</x:v>
       </x:c>
       <x:c r="D2" s="14" t="str">
-        <x:v>优惠报价场景</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" ht="40" customHeight="1">
+        <x:v>场景CSV与页面显示状态</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="44" customHeight="1">
       <x:c r="A3" s="13" t="str">
         <x:v>case_results.csv</x:v>
       </x:c>
       <x:c r="B3" s="13" t="str">
-        <x:v>P02的final_state</x:v>
-      </x:c>
-      <x:c r="C3" s="17" t="str">
-        <x:v>needs_vat</x:v>
+        <x:v>continue_enabled</x:v>
+      </x:c>
+      <x:c r="C3" s="13" t="str">
+        <x:v>按case_id与场景表对应布尔值比对</x:v>
       </x:c>
       <x:c r="D3" s="13" t="str">
-        <x:v>欧盟团队套餐场景</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" ht="40" customHeight="1">
+        <x:v>页面按钮可用性</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="44" customHeight="1">
       <x:c r="A4" s="15" t="str">
         <x:v>case_results.csv</x:v>
       </x:c>
       <x:c r="B4" s="15" t="str">
-        <x:v>P03的final_state</x:v>
-      </x:c>
-      <x:c r="C4" s="18" t="str">
-        <x:v>blocked_age</x:v>
+        <x:v>total_cents</x:v>
+      </x:c>
+      <x:c r="C4" s="15" t="str">
+        <x:v>按case_id与场景表对应分值比对</x:v>
       </x:c>
       <x:c r="D4" s="15" t="str">
-        <x:v>学生年龄限制场景</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="40" customHeight="1">
+        <x:v>页面总价</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="44" customHeight="1">
       <x:c r="A5" s="13" t="str">
         <x:v>case_results.csv</x:v>
       </x:c>
       <x:c r="B5" s="13" t="str">
-        <x:v>P04的final_state</x:v>
-      </x:c>
-      <x:c r="C5" s="17" t="str">
-        <x:v>payment_unavailable</x:v>
+        <x:v>banner_text</x:v>
+      </x:c>
+      <x:c r="C5" s="13" t="str">
+        <x:v>按case_id与场景表对应文本比对</x:v>
       </x:c>
       <x:c r="D5" s="13" t="str">
-        <x:v>地区支付限制场景</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="40" customHeight="1">
+        <x:v>页面状态提示</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="44" customHeight="1">
       <x:c r="A6" s="15" t="str">
         <x:v>case_results.csv</x:v>
       </x:c>
       <x:c r="B6" s="15" t="str">
-        <x:v>P05的final_state</x:v>
-      </x:c>
-      <x:c r="C6" s="18" t="str">
-        <x:v>manual_review</x:v>
+        <x:v>browser_time</x:v>
+      </x:c>
+      <x:c r="C6" s="15" t="str">
+        <x:v>与policy/test_contract.json中fixed_browser_time表示的UTC时间比对</x:v>
       </x:c>
       <x:c r="D6" s="15" t="str">
-        <x:v>企业审核场景</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="40" customHeight="1">
+        <x:v>浏览器内Date结果</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="44" customHeight="1">
       <x:c r="A7" s="13" t="str">
-        <x:v>case_results.csv</x:v>
+        <x:v>network_contract.csv</x:v>
       </x:c>
       <x:c r="B7" s="13" t="str">
-        <x:v>P06的final_state</x:v>
-      </x:c>
-      <x:c r="C7" s="17" t="str">
-        <x:v>ready</x:v>
+        <x:v>first_status和final_status</x:v>
+      </x:c>
+      <x:c r="C7" s="13" t="str">
+        <x:v>按case_id与quote_responses.json中status的首尾元素比对</x:v>
       </x:c>
       <x:c r="D7" s="13" t="str">
-        <x:v>过期报价重试场景</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="40" customHeight="1">
+        <x:v>实际route响应顺序</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="44" customHeight="1">
       <x:c r="A8" s="15" t="str">
         <x:v>network_contract.csv</x:v>
       </x:c>
       <x:c r="B8" s="15" t="str">
-        <x:v>P06的first_status</x:v>
-      </x:c>
-      <x:c r="C8" s="18" t="n">
-        <x:v>409</x:v>
+        <x:v>final_plan到final_payment</x:v>
+      </x:c>
+      <x:c r="C8" s="15" t="str">
+        <x:v>按case_id与场景CSV的请求字段比对</x:v>
       </x:c>
       <x:c r="D8" s="15" t="str">
-        <x:v>报价fixture状态序列</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="40" customHeight="1">
+        <x:v>最后一次报价请求</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="44" customHeight="1">
       <x:c r="A9" s="13" t="str">
-        <x:v>network_contract.csv</x:v>
+        <x:v>evidence_manifest.csv</x:v>
       </x:c>
       <x:c r="B9" s="13" t="str">
-        <x:v>P06的final_status</x:v>
-      </x:c>
-      <x:c r="C9" s="17" t="n">
-        <x:v>200</x:v>
+        <x:v>trace_file和screenshot_file</x:v>
+      </x:c>
+      <x:c r="C9" s="13" t="str">
+        <x:v>路径从output开始且指向同case_id文件</x:v>
       </x:c>
       <x:c r="D9" s="13" t="str">
-        <x:v>报价fixture状态序列</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="40" customHeight="1">
+        <x:v>Playwright产生的trace和截图</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="44" customHeight="1">
       <x:c r="A10" s="15" t="str">
-        <x:v>network_contract.csv</x:v>
+        <x:v>run_summary.json</x:v>
       </x:c>
       <x:c r="B10" s="15" t="str">
-        <x:v>P06的stale_retry_count</x:v>
-      </x:c>
-      <x:c r="C10" s="18" t="n">
-        <x:v>1</x:v>
+        <x:v>case_outcomes</x:v>
+      </x:c>
+      <x:c r="C10" s="15" t="str">
+        <x:v>按case_id与case_results.csv中final_state比对</x:v>
       </x:c>
       <x:c r="D10" s="15" t="str">
-        <x:v>过期报价重试</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" ht="40" customHeight="1">
-      <x:c r="A11" s="13" t="str">
-        <x:v>run_summary.json</x:v>
-      </x:c>
-      <x:c r="B11" s="13" t="str">
-        <x:v>fixed_browser_time</x:v>
-      </x:c>
-      <x:c r="C11" s="19" t="n">
-        <x:v>46233.395833333336</x:v>
-      </x:c>
-      <x:c r="D11" s="13" t="str">
-        <x:v>test_contract.json</x:v>
+        <x:v>发布回归摘要</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -707,72 +668,72 @@
     </x:row>
     <x:row r="2" ht="50" customHeight="1">
       <x:c r="A2" s="14" t="str">
-        <x:v>全部场景</x:v>
+        <x:v>场景结果范围</x:v>
       </x:c>
       <x:c r="B2" s="14" t="str">
-        <x:v>case_id</x:v>
+        <x:v>final_state</x:v>
       </x:c>
       <x:c r="C2" s="14" t="str">
-        <x:v>P01_PRO_MONTHLY_COUPON；P02_TEAM_EU_VAT；P03_STUDENT_AGE_LOCK；P04_STARTER_PAYPAL_REGION；P05_ENTERPRISE_APPROVAL；P06_PRO_RETRY_STALE</x:v>
+        <x:v>ready；needs_vat；blocked_age；payment_unavailable；manual_review</x:v>
       </x:c>
       <x:c r="D2" s="14" t="str">
-        <x:v>场景CSV</x:v>
+        <x:v>场景CSV的状态列</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="50" customHeight="1">
       <x:c r="A3" s="13" t="str">
-        <x:v>继续按钮可用场景</x:v>
+        <x:v>报价请求字段</x:v>
       </x:c>
       <x:c r="B3" s="13" t="str">
-        <x:v>case_id</x:v>
+        <x:v>query</x:v>
       </x:c>
       <x:c r="C3" s="13" t="str">
-        <x:v>P01_PRO_MONTHLY_COUPON；P06_PRO_RETRY_STALE</x:v>
+        <x:v>plan；seats；region；coupon；payment</x:v>
       </x:c>
       <x:c r="D3" s="13" t="str">
-        <x:v>页面结果</x:v>
+        <x:v>本地结账页的报价接口</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="50" customHeight="1">
       <x:c r="A4" s="15" t="str">
-        <x:v>继续按钮禁用场景</x:v>
+        <x:v>稳定定位方式</x:v>
       </x:c>
       <x:c r="B4" s="15" t="str">
-        <x:v>case_id</x:v>
+        <x:v>locator</x:v>
       </x:c>
       <x:c r="C4" s="15" t="str">
-        <x:v>P02_TEAM_EU_VAT；P03_STUDENT_AGE_LOCK；P04_STARTER_PAYPAL_REGION；P05_ENTERPRISE_APPROVAL</x:v>
+        <x:v>role；label；test id</x:v>
       </x:c>
       <x:c r="D4" s="15" t="str">
-        <x:v>页面结果</x:v>
+        <x:v>页面的可访问名称与测试属性</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="50" customHeight="1">
       <x:c r="A5" s="13" t="str">
-        <x:v>两次报价请求场景</x:v>
+        <x:v>场景证据类型</x:v>
       </x:c>
       <x:c r="B5" s="13" t="str">
-        <x:v>case_id</x:v>
+        <x:v>artifact</x:v>
       </x:c>
       <x:c r="C5" s="13" t="str">
-        <x:v>P02_TEAM_EU_VAT；P04_STARTER_PAYPAL_REGION；P05_ENTERPRISE_APPROVAL；P06_PRO_RETRY_STALE</x:v>
+        <x:v>trace ZIP；完整页面PNG</x:v>
       </x:c>
       <x:c r="D5" s="13" t="str">
-        <x:v>支付方式交互与过期重试</x:v>
+        <x:v>产品与测试评审需求</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="50" customHeight="1">
       <x:c r="A6" s="15" t="str">
-        <x:v>证据扩展名</x:v>
+        <x:v>发布报表</x:v>
       </x:c>
       <x:c r="B6" s="15" t="str">
-        <x:v>case_id</x:v>
+        <x:v>report</x:v>
       </x:c>
       <x:c r="C6" s="15" t="str">
-        <x:v>trace为.zip；截图为.png</x:v>
+        <x:v>case_results.csv；network_contract.csv；evidence_manifest.csv；run_summary.json</x:v>
       </x:c>
       <x:c r="D6" s="15" t="str">
-        <x:v>evidence_manifest.csv</x:v>
+        <x:v>任务Prompt声明的业务交付路径</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -785,10 +746,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="40" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="46" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="14" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="40" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="62" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="12" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="42" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="46" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
@@ -799,217 +760,132 @@
         <x:v>指标</x:v>
       </x:c>
       <x:c r="C1" s="6" t="str">
-        <x:v>正确值</x:v>
+        <x:v>判定方法</x:v>
       </x:c>
       <x:c r="D1" s="6" t="str">
         <x:v>单位</x:v>
       </x:c>
       <x:c r="E1" s="6" t="str">
-        <x:v>容差与来源</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" ht="36" customHeight="1">
+        <x:v>容差与业务依据</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="42" customHeight="1">
       <x:c r="A2" s="14" t="str">
-        <x:v>run_summary.json</x:v>
+        <x:v>case_results.csv</x:v>
       </x:c>
       <x:c r="B2" s="14" t="str">
-        <x:v>case_count</x:v>
-      </x:c>
-      <x:c r="C2" s="20" t="n">
-        <x:v>6</x:v>
+        <x:v>total_cents</x:v>
+      </x:c>
+      <x:c r="C2" s="14" t="str">
+        <x:v>按case_id与场景CSV对应值相等</x:v>
       </x:c>
       <x:c r="D2" s="14" t="str">
-        <x:v>项</x:v>
+        <x:v>分</x:v>
       </x:c>
       <x:c r="E2" s="14" t="str">
-        <x:v>无容差；场景CSV</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" ht="36" customHeight="1">
+        <x:v>无容差；页面展示的报价</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="42" customHeight="1">
       <x:c r="A3" s="13" t="str">
-        <x:v>run_summary.json</x:v>
+        <x:v>case_results.csv</x:v>
       </x:c>
       <x:c r="B3" s="13" t="str">
-        <x:v>enabled_case_count</x:v>
-      </x:c>
-      <x:c r="C3" s="21" t="n">
-        <x:v>2</x:v>
+        <x:v>intercept_count</x:v>
+      </x:c>
+      <x:c r="C3" s="13" t="str">
+        <x:v>按case_id与场景CSV对应值相等</x:v>
       </x:c>
       <x:c r="D3" s="13" t="str">
-        <x:v>项</x:v>
+        <x:v>次</x:v>
       </x:c>
       <x:c r="E3" s="13" t="str">
-        <x:v>无容差；页面按钮状态</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" ht="36" customHeight="1">
+        <x:v>无容差；实际route调用</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="42" customHeight="1">
       <x:c r="A4" s="15" t="str">
-        <x:v>run_summary.json</x:v>
+        <x:v>case_results.csv</x:v>
       </x:c>
       <x:c r="B4" s="15" t="str">
-        <x:v>disabled_case_count</x:v>
-      </x:c>
-      <x:c r="C4" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>focus_check_count</x:v>
+      </x:c>
+      <x:c r="C4" s="15" t="str">
+        <x:v>等于该场景实际执行的焦点断言数</x:v>
       </x:c>
       <x:c r="D4" s="15" t="str">
-        <x:v>项</x:v>
+        <x:v>次</x:v>
       </x:c>
       <x:c r="E4" s="15" t="str">
-        <x:v>无容差；页面按钮状态</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="36" customHeight="1">
+        <x:v>无容差；Playwright焦点断言</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="42" customHeight="1">
       <x:c r="A5" s="13" t="str">
-        <x:v>run_summary.json</x:v>
+        <x:v>network_contract.csv</x:v>
       </x:c>
       <x:c r="B5" s="13" t="str">
-        <x:v>total_intercepts</x:v>
-      </x:c>
-      <x:c r="C5" s="21" t="n">
-        <x:v>10</x:v>
+        <x:v>request_count</x:v>
+      </x:c>
+      <x:c r="C5" s="13" t="str">
+        <x:v>等于该case_id的实际报价请求记录数</x:v>
       </x:c>
       <x:c r="D5" s="13" t="str">
         <x:v>次</x:v>
       </x:c>
       <x:c r="E5" s="13" t="str">
-        <x:v>无容差；报价route调用</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="36" customHeight="1">
+        <x:v>无容差；route记录</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="42" customHeight="1">
       <x:c r="A6" s="15" t="str">
-        <x:v>run_summary.json</x:v>
+        <x:v>network_contract.csv</x:v>
       </x:c>
       <x:c r="B6" s="15" t="str">
-        <x:v>trace_zip_count</x:v>
-      </x:c>
-      <x:c r="C6" s="22" t="n">
-        <x:v>6</x:v>
+        <x:v>stale_retry_count</x:v>
+      </x:c>
+      <x:c r="C6" s="15" t="str">
+        <x:v>等于该case_id中状态码409的响应数</x:v>
       </x:c>
       <x:c r="D6" s="15" t="str">
+        <x:v>次</x:v>
+      </x:c>
+      <x:c r="E6" s="15" t="str">
+        <x:v>无容差；fixture响应顺序</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="42" customHeight="1">
+      <x:c r="A7" s="13" t="str">
+        <x:v>evidence_manifest.csv</x:v>
+      </x:c>
+      <x:c r="B7" s="13" t="str">
+        <x:v>证据文件数</x:v>
+      </x:c>
+      <x:c r="C7" s="13" t="str">
+        <x:v>每个case_id对应一份trace和一张截图</x:v>
+      </x:c>
+      <x:c r="D7" s="13" t="str">
         <x:v>份</x:v>
       </x:c>
-      <x:c r="E6" s="15" t="str">
-        <x:v>无容差；trace目录</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="36" customHeight="1">
-      <x:c r="A7" s="13" t="str">
-        <x:v>run_summary.json</x:v>
-      </x:c>
-      <x:c r="B7" s="13" t="str">
-        <x:v>screenshot_count</x:v>
-      </x:c>
-      <x:c r="C7" s="21" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D7" s="13" t="str">
-        <x:v>张</x:v>
-      </x:c>
       <x:c r="E7" s="13" t="str">
-        <x:v>无容差；截图目录</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="36" customHeight="1">
+        <x:v>无容差；实际证据目录</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="42" customHeight="1">
       <x:c r="A8" s="15" t="str">
         <x:v>run_summary.json</x:v>
       </x:c>
       <x:c r="B8" s="15" t="str">
-        <x:v>focus_check_count</x:v>
-      </x:c>
-      <x:c r="C8" s="22" t="n">
-        <x:v>20</x:v>
+        <x:v>场景数</x:v>
+      </x:c>
+      <x:c r="C8" s="15" t="str">
+        <x:v>等于场景CSV中唯一case_id的数量</x:v>
       </x:c>
       <x:c r="D8" s="15" t="str">
-        <x:v>次</x:v>
+        <x:v>项</x:v>
       </x:c>
       <x:c r="E8" s="15" t="str">
-        <x:v>无容差；页面焦点断言</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="36" customHeight="1">
-      <x:c r="A9" s="13" t="str">
-        <x:v>case_results.csv</x:v>
-      </x:c>
-      <x:c r="B9" s="13" t="str">
-        <x:v>P01的total_cents</x:v>
-      </x:c>
-      <x:c r="C9" s="21" t="n">
-        <x:v>1600</x:v>
-      </x:c>
-      <x:c r="D9" s="13" t="str">
-        <x:v>分</x:v>
-      </x:c>
-      <x:c r="E9" s="13" t="str">
-        <x:v>无容差；优惠报价</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="36" customHeight="1">
-      <x:c r="A10" s="15" t="str">
-        <x:v>case_results.csv</x:v>
-      </x:c>
-      <x:c r="B10" s="15" t="str">
-        <x:v>P02的total_cents</x:v>
-      </x:c>
-      <x:c r="C10" s="22" t="n">
-        <x:v>71400</x:v>
-      </x:c>
-      <x:c r="D10" s="15" t="str">
-        <x:v>分</x:v>
-      </x:c>
-      <x:c r="E10" s="15" t="str">
-        <x:v>无容差；团队套餐报价</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" ht="36" customHeight="1">
-      <x:c r="A11" s="13" t="str">
-        <x:v>case_results.csv</x:v>
-      </x:c>
-      <x:c r="B11" s="13" t="str">
-        <x:v>P04的total_cents</x:v>
-      </x:c>
-      <x:c r="C11" s="21" t="n">
-        <x:v>1200</x:v>
-      </x:c>
-      <x:c r="D11" s="13" t="str">
-        <x:v>分</x:v>
-      </x:c>
-      <x:c r="E11" s="13" t="str">
-        <x:v>无容差；Starter报价</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" ht="36" customHeight="1">
-      <x:c r="A12" s="15" t="str">
-        <x:v>case_results.csv</x:v>
-      </x:c>
-      <x:c r="B12" s="15" t="str">
-        <x:v>P06的total_cents</x:v>
-      </x:c>
-      <x:c r="C12" s="22" t="n">
-        <x:v>2500</x:v>
-      </x:c>
-      <x:c r="D12" s="15" t="str">
-        <x:v>分</x:v>
-      </x:c>
-      <x:c r="E12" s="15" t="str">
-        <x:v>无容差；刷新后报价</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" ht="36" customHeight="1">
-      <x:c r="A13" s="13" t="str">
-        <x:v>策略变化运行</x:v>
-      </x:c>
-      <x:c r="B13" s="13" t="str">
-        <x:v>fixed_browser_time改为10:00后的匹配场景数</x:v>
-      </x:c>
-      <x:c r="C13" s="21" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D13" s="13" t="str">
-        <x:v>项</x:v>
-      </x:c>
-      <x:c r="E13" s="13" t="str">
-        <x:v>无容差；浏览器内Date结果</x:v>
+        <x:v>无容差；场景CSV</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1097,10 +973,10 @@
         <x:v>代码排版</x:v>
       </x:c>
       <x:c r="B7" s="13" t="str">
-        <x:v>空白、注释、单双引号和等价语法不计分</x:v>
+        <x:v>空白、注释和等价语法不计分</x:v>
       </x:c>
       <x:c r="C7" s="13" t="str">
-        <x:v>语法错误、运行失败或业务结果变化不属于允许变体</x:v>
+        <x:v>语法错误或业务结果改变不属于允许变体</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="52" customHeight="1">
